--- a/media/exports/reports/2026-07/people-helped.xlsx
+++ b/media/exports/reports/2026-07/people-helped.xlsx
@@ -859,7 +859,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>How many people did we help this month, and how many couldn't we reach?</t>
+          <t>How many people did you help this month, and how many couldn't you reach?</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: July 2026 · Data status: Jun 2026 locked · Jul 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
+          <t>Period: July 2026 · Data status: Jul 2026 locked (data retrieved 2pm, Tue 6 Oct 2026) · Generated 22 Oct 2026, 4:57pm</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1192,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 people-helped.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 people-helped.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 22 Oct 2026, 4:57pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1237,7 +1237,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: July 2026 · Data status: Jun 2026 locked · Jul 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
+          <t>Period: July 2026 · Data status: Jul 2026 locked (data retrieved 2pm, Tue 6 Oct 2026) · Generated 22 Oct 2026, 4:57pm</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>People we couldn't reach</t>
+          <t>People not reached</t>
         </is>
       </c>
       <c r="B9" s="16" t="n">
@@ -1355,7 +1355,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>People we couldn't reach</t>
+          <t>People not reached</t>
         </is>
       </c>
       <c r="B17" s="16" t="n">
@@ -1425,7 +1425,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>People we couldn't reach</t>
+          <t>People not reached</t>
         </is>
       </c>
       <c r="B25" s="16" t="n">
@@ -1734,7 +1734,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 people-helped.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 people-helped.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 22 Oct 2026, 4:57pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1825,7 +1825,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: July 2026 · Data status: Jun 2026 locked · Jul 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
+          <t>Period: July 2026 · Data status: Jul 2026 locked (data retrieved 2pm, Tue 6 Oct 2026) · Generated 22 Oct 2026, 4:57pm</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 people-helped.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 people-helped.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 22 Oct 2026, 4:57pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
